--- a/LITE_PANT_RANGO_PRODUCCION.xlsx
+++ b/LITE_PANT_RANGO_PRODUCCION.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Verde — unidades (máx tela)</t>
+          <t>Verde — unidades mín (÷1.3)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1054,11 +1054,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Negro — unidades (÷1.3 margen +30%)</t>
+          <t>Verde — unidades máx (100% tela)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>606</v>
+        <v>299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1069,11 +1069,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Negro — unidades (uso total tela asignada)</t>
+          <t>Negro — unidades mín (÷1.15)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>788</v>
+        <v>685</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1084,94 +1084,96 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Consumo prom. VIORI/pieza (curva tallas)</t>
+          <t>Negro — unidades máx (100% tela)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.5429</v>
+        <v>788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mts</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Consumo prom. VIORI/pieza (curva tallas)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.5429</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Vinotinto</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>NO COMPRADO</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>── COLORES DE PRODUCCIÓN ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>606</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>mín und · máx 788</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Verde Militar</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>299</v>
+        <v>685</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>und (máx tela verde)</t>
+          <t>mín · máx 788 und</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Curva completa color × talla</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Hoja Cantidades por Colores</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>230</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mín · máx 299 und</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Detalle color/talla Mín-Máx</t>
+          <t>Curva completa color × talla</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hoja Producción Color × Talla</t>
+          <t>Hoja Cantidades por Colores</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1179,134 +1181,132 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Detalle color/talla Mín-Máx</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hoja Producción Color × Talla</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Compra tela VIORI</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Hoja Compra de Tela (+20% SS)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>── AJUSTE CURVA TALLAS ──</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Curva histórica (BASIC LINE PANT)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Dashboard Basic Line</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>M objetivo</t>
+          <t>Curva histórica (BASIC LINE PANT)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>hist 30.1%</t>
-        </is>
-      </c>
+          <t>Dashboard Basic Line</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S objetivo</t>
+          <t>M objetivo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hist 28.0%</t>
+          <t>hist 30.1%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>XS (recibe resto M+S)</t>
+          <t>S objetivo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>hist 14.0%</t>
+          <t>hist 28.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>XS (recibe resto M+S)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>hist 14.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>XL (+1.5 pp ← L)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>XL 11.3%</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>L 16.6% · XS sin cambio</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>── AJUSTES DE TIENDA (DISTRIBUCIÓN) ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Tolón histórico</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>und/mes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tolón proyectado (85% Chacao)</t>
+          <t>Tolón histórico</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1317,11 +1317,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Web histórica</t>
+          <t>Tolón proyectado (85% Chacao)</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1332,11 +1332,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Web proyectada (60% Cerro Verde)</t>
+          <t>Web histórica</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>La Vela histórica</t>
+          <t>Web proyectada (60% Cerro Verde)</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1362,11 +1362,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>La Vela proyectada (avg Sambil + Cerro Verde)</t>
+          <t>La Vela histórica</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1377,11 +1377,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Grand Plaz histórica</t>
+          <t>La Vela proyectada (avg Sambil + Cerro Verde)</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Grand Plaz proyectada (+68% hist.)</t>
+          <t>Grand Plaz histórica</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1407,11 +1407,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Barquisimeto (avg Grieta+Chacao+Tolón proy.)</t>
+          <t>Grand Plaz proyectada (+68% hist.)</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1422,45 +1422,60 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>Barquisimeto (avg Grieta+Chacao+Tolón proy.)</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>und/mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Corporativo</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>EXCLUIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>• Referencia: BASIC LINE PANT DAMA del dashboard Basic Line.</t>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>• Producto NUEVO manufacturado — sin stock inicial.</t>
+          <t>• Referencia: BASIC LINE PANT DAMA del dashboard Basic Line.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>• Solo género DAMA, tallas XS a XL.</t>
+          <t>• Producto NUEVO manufacturado — sin stock inicial.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
+        <is>
+          <t>• Solo género DAMA, tallas XS a XL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>• Compra tela VIORI incluye +20% stock de seguridad.</t>
         </is>
@@ -1535,7 +1550,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>272</v>
@@ -1553,7 +1568,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>239</v>
@@ -1571,7 +1586,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>272</v>
@@ -1589,7 +1604,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>181</v>
@@ -1607,7 +1622,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>123</v>
@@ -1620,7 +1635,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>1087</v>
@@ -1667,14 +1682,14 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Rango producción: 905 – 1087 und</t>
+          <t>Rango producción: 915 – 1087 und</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>MÍNIMO — 905 und (compromiso)</t>
+          <t>MÍNIMO — 915 und (compromiso)</t>
         </is>
       </c>
     </row>
@@ -1722,22 +1737,22 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>606</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -1747,22 +1762,22 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>299</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -1772,22 +1787,22 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
     </row>
     <row r="11">
@@ -1950,7 +1965,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>934.91</v>
+        <v>1056.91</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>1215.88</v>
@@ -1973,7 +1988,7 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>461.21</v>
+        <v>354.66</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>461.21</v>
@@ -1996,7 +2011,7 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>1396.12</v>
+        <v>1411.57</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>1677.09</v>
@@ -2019,7 +2034,7 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>644.01</v>
+        <v>651.08</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>773.45</v>
@@ -2042,7 +2057,7 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>1087</v>
@@ -2109,7 +2124,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Rango global: 905 – 1087 und</t>
+          <t>Rango global: 915 – 1087 und</t>
         </is>
       </c>
     </row>
@@ -2211,31 +2226,31 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>197</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>173</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>197</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>131</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>90</v>
@@ -2248,7 +2263,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>606</v>
+        <v>685</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>788</v>
@@ -2352,31 +2367,31 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>75</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>66</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>75</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>50</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>33</v>
@@ -2389,7 +2404,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>299</v>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>1087</v>
@@ -2422,7 +2437,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>606</v>
+        <v>685</v>
       </c>
       <c r="C20" t="n">
         <v>788</v>
@@ -2435,7 +2450,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="C21" t="n">
         <v>299</v>
@@ -2559,25 +2574,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>606</v>
+        <v>685</v>
       </c>
       <c r="D5" t="n">
         <v>788</v>
       </c>
       <c r="E5" t="n">
-        <v>934.91</v>
+        <v>1056.91</v>
       </c>
       <c r="F5" t="n">
         <v>1215.88</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>934.91</v>
+        <v>1056.91</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>1215.88</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>107.755</v>
+        <v>121.84</v>
       </c>
       <c r="J5" s="23" t="n">
         <v>140.167</v>
@@ -2595,25 +2610,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="D6" t="n">
         <v>299</v>
       </c>
       <c r="E6" t="n">
-        <v>461.21</v>
+        <v>354.66</v>
       </c>
       <c r="F6" t="n">
         <v>461.21</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>461.21</v>
+        <v>354.66</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>461.21</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>53.15</v>
+        <v>40.864</v>
       </c>
       <c r="J6" s="23" t="n">
         <v>53.15</v>
@@ -2626,25 +2641,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="D7" t="n">
         <v>1087</v>
       </c>
       <c r="E7" t="n">
-        <v>1396.12</v>
+        <v>1411.57</v>
       </c>
       <c r="F7" t="n">
         <v>1677.09</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1396.12</v>
+        <v>1411.57</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>1677.09</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>160.905</v>
+        <v>162.704</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>193.317</v>
@@ -2874,7 +2889,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>644.01</v>
+        <v>651.08</v>
       </c>
       <c r="C20" t="n">
         <v>773.45</v>
@@ -2887,7 +2902,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="C21" t="n">
         <v>1087</v>
@@ -3034,7 +3049,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>22</v>
@@ -3065,7 +3080,7 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="23" t="n">
         <v>62</v>
@@ -3077,7 +3092,7 @@
         <v>54</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>62</v>
@@ -3089,7 +3104,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>28</v>
@@ -3120,7 +3135,7 @@
         <v>37</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="23" t="n">
         <v>24</v>
@@ -3139,7 +3154,7 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="23" t="n">
         <v>30</v>
@@ -3151,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>30</v>
@@ -3163,7 +3178,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8" s="23" t="n">
         <v>14</v>
@@ -3237,7 +3252,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>14</v>
@@ -3274,7 +3289,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="23" t="n">
         <v>11</v>
@@ -3336,7 +3351,7 @@
         <v>34</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>39</v>
@@ -3348,7 +3363,7 @@
         <v>26</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" s="23" t="n">
         <v>18</v>
@@ -3361,31 +3376,31 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>272</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>238</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>272</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>181</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>124</v>
@@ -3427,7 +3442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="n">
         <v>101</v>
@@ -3443,7 +3458,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C19" t="n">
         <v>247</v>
@@ -3459,7 +3474,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" t="n">
         <v>147</v>
@@ -3475,7 +3490,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" t="n">
         <v>121</v>
@@ -3507,7 +3522,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="n">
         <v>124</v>
@@ -3523,7 +3538,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" t="n">
         <v>103</v>
@@ -3555,7 +3570,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C26" t="n">
         <v>156</v>
@@ -3648,7 +3663,7 @@
         <v>67</v>
       </c>
       <c r="C6" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D6" t="n">
         <v>272</v>
@@ -3664,7 +3679,7 @@
         <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D7" t="n">
         <v>239</v>
@@ -3680,7 +3695,7 @@
         <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D8" t="n">
         <v>272</v>
@@ -3696,7 +3711,7 @@
         <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -3712,7 +3727,7 @@
         <v>77</v>
       </c>
       <c r="C10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="n">
         <v>123</v>
@@ -3726,7 +3741,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>644.01</v>
+        <v>651.08</v>
       </c>
       <c r="D12" t="n">
         <v>773.45</v>
@@ -3768,7 +3783,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3830,7 +3845,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>905 – 1087 und</t>
+          <t>915 – 1087 und</t>
         </is>
       </c>
     </row>

--- a/LITE_PANT_RANGO_PRODUCCION.xlsx
+++ b/LITE_PANT_RANGO_PRODUCCION.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5429</v>
+        <v>1.5425</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1283,45 +1283,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XL 11.3%</t>
+          <t>XL 11.0%</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L 16.6% · XS sin cambio</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+          <t>L 16.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Núcleo S+M (+0.75 pp c/u)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S 22.8% · M 25.8%</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Descuento proporcional XS/L/XL · criterio I+D</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>── AJUSTES DE TIENDA (DISTRIBUCIÓN) ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Tolón histórico</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>und/mes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tolón proyectado (85% Chacao)</t>
+          <t>Tolón histórico</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1332,11 +1334,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Web histórica</t>
+          <t>Tolón proyectado (85% Chacao)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1347,11 +1349,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Web proyectada (60% Cerro Verde)</t>
+          <t>Web histórica</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1362,11 +1364,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>La Vela histórica</t>
+          <t>Web proyectada (60% Cerro Verde)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1377,11 +1379,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>La Vela proyectada (avg Sambil + Cerro Verde)</t>
+          <t>La Vela histórica</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1392,11 +1394,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Grand Plaz histórica</t>
+          <t>La Vela proyectada (avg Sambil + Cerro Verde)</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1407,7 +1409,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Grand Plaz proyectada (+68% hist.)</t>
+          <t>Grand Plaz histórica</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1422,11 +1424,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Barquisimeto (avg Grieta+Chacao+Tolón proy.)</t>
+          <t>Grand Plaz proyectada (+68% hist.)</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1437,45 +1439,60 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Barquisimeto (avg Grieta+Chacao+Tolón proy.)</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>und/mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Corporativo</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>EXCLUIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>• Referencia: BASIC LINE PANT DAMA del dashboard Basic Line.</t>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>• Producto NUEVO manufacturado — sin stock inicial.</t>
+          <t>• Referencia: BASIC LINE PANT DAMA del dashboard Basic Line.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>• Solo género DAMA, tallas XS a XL.</t>
+          <t>• Producto NUEVO manufacturado — sin stock inicial.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
+        <is>
+          <t>• Solo género DAMA, tallas XS a XL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>• Compra tela VIORI incluye +20% stock de seguridad.</t>
         </is>
@@ -1546,14 +1563,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
@@ -1564,14 +1581,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -1582,14 +1599,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
@@ -1600,14 +1617,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
@@ -1618,14 +1635,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -1737,19 +1754,19 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>685</v>
@@ -1762,19 +1779,19 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>230</v>
@@ -1787,19 +1804,19 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>915</v>
@@ -1856,19 +1873,19 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>788</v>
@@ -1881,16 +1898,16 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F14" s="17" t="n">
         <v>33</v>
@@ -1906,19 +1923,19 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>1087</v>
@@ -1965,10 +1982,10 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>1056.91</v>
+        <v>1056.54</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>1215.88</v>
+        <v>1215.49</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1988,10 +2005,10 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>354.66</v>
+        <v>354.85</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>461.21</v>
+        <v>461.17</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2011,10 +2028,10 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>1411.57</v>
+        <v>1411.39</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>1677.09</v>
+        <v>1676.66</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2023,7 +2040,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>193.317 kg al máx · consumo = tela disponible</t>
+          <t>193.214 kg al máx · consumo = tela disponible</t>
         </is>
       </c>
     </row>
@@ -2034,10 +2051,10 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>651.08</v>
+        <v>650.95</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>773.45</v>
+        <v>773.3099999999999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2226,34 +2243,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -2367,31 +2384,31 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>33</v>
@@ -2580,22 +2597,22 @@
         <v>788</v>
       </c>
       <c r="E5" t="n">
-        <v>1056.91</v>
+        <v>1056.54</v>
       </c>
       <c r="F5" t="n">
-        <v>1215.88</v>
+        <v>1215.49</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1056.91</v>
+        <v>1056.54</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1215.88</v>
+        <v>1215.49</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>121.84</v>
+        <v>121.746</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>140.167</v>
+        <v>140.07</v>
       </c>
     </row>
     <row r="6">
@@ -2616,22 +2633,22 @@
         <v>299</v>
       </c>
       <c r="E6" t="n">
-        <v>354.66</v>
+        <v>354.85</v>
       </c>
       <c r="F6" t="n">
-        <v>461.21</v>
+        <v>461.17</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>354.66</v>
+        <v>354.85</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>461.21</v>
+        <v>461.17</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>40.864</v>
+        <v>40.902</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>53.15</v>
+        <v>53.144</v>
       </c>
     </row>
     <row r="7">
@@ -2647,22 +2664,22 @@
         <v>1087</v>
       </c>
       <c r="E7" t="n">
-        <v>1411.57</v>
+        <v>1411.39</v>
       </c>
       <c r="F7" t="n">
-        <v>1677.09</v>
+        <v>1676.66</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1411.57</v>
+        <v>1411.39</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>1677.09</v>
+        <v>1676.66</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>162.704</v>
+        <v>162.648</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>193.317</v>
+        <v>193.214</v>
       </c>
     </row>
     <row r="9">
@@ -2731,31 +2748,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E11" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
         <v>788</v>
       </c>
       <c r="H11" t="n">
-        <v>1215.88</v>
+        <v>1215.49</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1215.88</v>
+        <v>1215.49</v>
       </c>
       <c r="J11" t="n">
-        <v>140.167</v>
+        <v>140.07</v>
       </c>
     </row>
     <row r="12">
@@ -2765,16 +2782,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
@@ -2783,13 +2800,13 @@
         <v>299</v>
       </c>
       <c r="H12" t="n">
-        <v>461.21</v>
+        <v>461.17</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>461.21</v>
+        <v>461.17</v>
       </c>
       <c r="J12" t="n">
-        <v>53.15</v>
+        <v>53.144</v>
       </c>
     </row>
     <row r="14">
@@ -2889,10 +2906,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>651.08</v>
+        <v>650.95</v>
       </c>
       <c r="C20" t="n">
-        <v>773.45</v>
+        <v>773.3099999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3052,25 +3069,25 @@
         <v>19</v>
       </c>
       <c r="E5" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="F5" s="22" t="n">
-        <v>21</v>
-      </c>
       <c r="G5" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="22" t="n">
         <v>14</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5" s="23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -3080,34 +3097,34 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="22" t="n">
         <v>23</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -3117,25 +3134,25 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="F7" s="22" t="n">
-        <v>31</v>
-      </c>
       <c r="G7" s="23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="23" t="n">
         <v>24</v>
@@ -3144,7 +3161,7 @@
         <v>14</v>
       </c>
       <c r="K7" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3154,34 +3171,34 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="22" t="n">
         <v>26</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>20</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -3231,28 +3248,28 @@
         <v>26</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="F10" s="22" t="n">
-        <v>26</v>
-      </c>
       <c r="G10" s="23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>17</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>14</v>
@@ -3265,13 +3282,13 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>23</v>
@@ -3280,7 +3297,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="22" t="n">
         <v>14</v>
@@ -3302,31 +3319,31 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="C12" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>18</v>
-      </c>
       <c r="G12" s="23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>12</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>10</v>
@@ -3339,28 +3356,28 @@
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="F13" s="22" t="n">
-        <v>33</v>
-      </c>
       <c r="G13" s="23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>15</v>
@@ -3376,34 +3393,34 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -3663,10 +3680,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D6" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7">
@@ -3679,10 +3696,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D7" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -3695,10 +3712,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D8" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
@@ -3711,10 +3728,10 @@
         <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -3727,10 +3744,10 @@
         <v>77</v>
       </c>
       <c r="C10" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -3741,10 +3758,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>651.08</v>
+        <v>650.95</v>
       </c>
       <c r="D12" t="n">
-        <v>773.45</v>
+        <v>773.3099999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3860,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -4080,112 +4097,119 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ajustada: M 25% · S 22% · XS 25.0% (recibe lo restado de M y S).</t>
+          <t xml:space="preserve">   Ajustada: M 25% · S 22% · XS 24.3% (recibe lo restado de M y S).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   XL reforzado +1.5 pp desde L → L 16.6% · XL 11.3% (XS sin cambio).</t>
+          <t xml:space="preserve">   XL reforzado +1.5 pp desde L → L 16.2% · XL 11.0%.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Núcleo S+M: +0.75 pp a S y a M (igual en chaqueta y pant); resto desde XS/L/XL proporcional.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>6. DISTRIBUCIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Por tienda: pesos mensuales proyectados (Tolón/Web/Barquisimeto ajustados).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Por tienda: pesos mensuales proyectados (Tolón/Web/Barquisimeto ajustados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Por talla: curva ajustada (ver sección 5).</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>7. COLORES Y COMPRA DE TELA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Colores producción: Negro 40% · Vinotinto 30% · Verde Militar 30%.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Dentro de cada color se aplica la misma curva de tallas.</t>
+          <t xml:space="preserve">   Colores producción: Negro 40% · Vinotinto 30% · Verde Militar 30%.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Consumo VIORI por pieza (ficha LITE PANT DAMA): XS 1.45m · S 1.48m · M 1.58m · L 1.63m · XL 1.66m.</t>
+          <t xml:space="preserve">   Dentro de cada color se aplica la misma curva de tallas.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stock de seguridad tela: +20% sobre consumo (compra = consumo × 1.2).</t>
+          <t xml:space="preserve">   Consumo VIORI por pieza (ficha LITE PANT DAMA): XS 1.45m · S 1.48m · M 1.58m · L 1.63m · XL 1.66m.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Stock de seguridad tela: +20% sobre consumo (compra = consumo × 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Ver hojas 'Producción Color × Talla' y 'Compra de Tela VIORI'.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>8. OTROS INSUMOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Elástica 4.5 cm: consumo por talla según ficha (67–77 cm/pieza).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Etiqueta agua/SENCAMER: 1 und/pieza · costado derecho.</t>
+          <t xml:space="preserve">   Elástica 4.5 cm: consumo por talla según ficha (67–77 cm/pieza).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Etiqueta agua/SENCAMER: 1 und/pieza · costado derecho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t xml:space="preserve">   Hilos: Negro-N · Vinotinto · Verde Militar (según color de tela).</t>
         </is>

--- a/LITE_PANT_RANGO_PRODUCCION.xlsx
+++ b/LITE_PANT_RANGO_PRODUCCION.xlsx
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5425</v>
+        <v>1.5485</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mín · máx 788 und</t>
+          <t>mín · máx 785 und</t>
         </is>
       </c>
     </row>
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mín · máx 299 und</t>
+          <t>mín · máx 298 und</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1283,29 +1283,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XL 11.0%</t>
+          <t>XL 11.3%</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L 16.2%</t>
+          <t>L 16.6%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Núcleo S+M (+0.75 pp c/u)</t>
+          <t>XS objetivo 18%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S 22.8% · M 25.8%</t>
+          <t>XS 18.0%</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Descuento proporcional XS/L/XL · criterio I+D</t>
+          <t>Exceso repartido 50/50 a S y M · L/XL sin cambio</t>
         </is>
       </c>
     </row>
@@ -1563,14 +1563,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>264</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>247</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
@@ -1599,14 +1599,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -1635,14 +1635,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -1699,14 +1699,14 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Rango producción: 915 – 1087 und</t>
+          <t>Rango producción: 912 – 1083 und</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>MÍNIMO — 915 und (compromiso)</t>
+          <t>MÍNIMO — 912 und (compromiso)</t>
         </is>
       </c>
     </row>
@@ -1754,22 +1754,22 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -1779,22 +1779,22 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -1804,28 +1804,28 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>MÁXIMO — 1087 und (techo)</t>
+          <t>MÁXIMO — 1083 und (techo)</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="14">
@@ -1898,22 +1898,22 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" s="17" t="n">
         <v>33</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -1923,22 +1923,22 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>265</v>
+        <v>195</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="17">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>1056.54</v>
+        <v>1057.61</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>1215.49</v>
+        <v>1215.64</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>354.85</v>
+        <v>354.75</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>461.17</v>
+        <v>461.36</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>1411.39</v>
+        <v>1412.36</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>1676.66</v>
+        <v>1677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>193.214 kg al máx · consumo = tela disponible</t>
+          <t>193.319 kg al máx · consumo = tela disponible</t>
         </is>
       </c>
     </row>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>650.95</v>
+        <v>651.16</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>773.3099999999999</v>
+        <v>773.28</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2141,14 +2141,14 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Rango global: 915 – 1087 und</t>
+          <t>Rango global: 912 – 1083 und</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Negro (788 und máx)</t>
+          <t>Negro (785 und máx)</t>
         </is>
       </c>
     </row>
@@ -2243,34 +2243,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -2280,16 +2280,16 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>Verde Militar (299 und máx)</t>
+          <t>Verde Militar (298 und máx)</t>
         </is>
       </c>
     </row>
@@ -2384,31 +2384,31 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>33</v>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="19">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C20" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="21">
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D5" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="E5" t="n">
-        <v>1056.54</v>
+        <v>1057.61</v>
       </c>
       <c r="F5" t="n">
-        <v>1215.49</v>
+        <v>1215.64</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1056.54</v>
+        <v>1057.61</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1215.49</v>
+        <v>1215.64</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>121.746</v>
+        <v>121.918</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>140.07</v>
+        <v>140.144</v>
       </c>
     </row>
     <row r="6">
@@ -2627,28 +2627,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E6" t="n">
-        <v>354.85</v>
+        <v>354.75</v>
       </c>
       <c r="F6" t="n">
-        <v>461.17</v>
+        <v>461.36</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>354.85</v>
+        <v>354.75</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>461.17</v>
+        <v>461.36</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>40.902</v>
+        <v>40.914</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>53.144</v>
+        <v>53.175</v>
       </c>
     </row>
     <row r="7">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D7" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="E7" t="n">
-        <v>1411.39</v>
+        <v>1412.36</v>
       </c>
       <c r="F7" t="n">
-        <v>1676.66</v>
+        <v>1677</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1411.39</v>
+        <v>1412.36</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>1676.66</v>
+        <v>1677</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>162.648</v>
+        <v>162.832</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>193.214</v>
+        <v>193.319</v>
       </c>
     </row>
     <row r="9">
@@ -2748,31 +2748,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" t="n">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="H11" t="n">
-        <v>1215.49</v>
+        <v>1215.64</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1215.49</v>
+        <v>1215.64</v>
       </c>
       <c r="J11" t="n">
-        <v>140.07</v>
+        <v>140.144</v>
       </c>
     </row>
     <row r="12">
@@ -2782,31 +2782,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H12" t="n">
-        <v>461.17</v>
+        <v>461.36</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>461.17</v>
+        <v>461.36</v>
       </c>
       <c r="J12" t="n">
-        <v>53.144</v>
+        <v>53.175</v>
       </c>
     </row>
     <row r="14">
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>650.95</v>
+        <v>651.16</v>
       </c>
       <c r="C20" t="n">
-        <v>773.3099999999999</v>
+        <v>773.28</v>
       </c>
     </row>
     <row r="21">
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C21" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -3060,31 +3060,31 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D5" s="22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H5" s="22" t="n">
         <v>14</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" s="23" t="n">
         <v>11</v>
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>40</v>
@@ -3124,7 +3124,7 @@
         <v>23</v>
       </c>
       <c r="K6" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -3134,25 +3134,25 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="23" t="n">
         <v>24</v>
@@ -3161,7 +3161,7 @@
         <v>14</v>
       </c>
       <c r="K7" s="23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C8" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" s="22" t="n">
         <v>29</v>
       </c>
-      <c r="D8" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>26</v>
-      </c>
       <c r="G8" s="23" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>20</v>
@@ -3198,7 +3198,7 @@
         <v>12</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -3245,28 +3245,28 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C10" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="F10" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>27</v>
-      </c>
       <c r="G10" s="23" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>17</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="22" t="n">
         <v>11</v>
@@ -3282,22 +3282,22 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C11" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="D11" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>22</v>
-      </c>
       <c r="G11" s="23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H11" s="22" t="n">
         <v>14</v>
@@ -3309,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -3319,31 +3319,31 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="F12" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="D12" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>19</v>
-      </c>
       <c r="G12" s="23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>12</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>10</v>
@@ -3356,28 +3356,28 @@
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>15</v>
@@ -3393,34 +3393,34 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -3478,7 +3478,7 @@
         <v>206</v>
       </c>
       <c r="C19" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D19" t="n">
         <v>10.7</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" t="n">
         <v>124</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" t="n">
         <v>103</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C26" t="n">
         <v>156</v>
@@ -3680,10 +3680,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="n">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="D6" t="n">
-        <v>264</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -3696,10 +3696,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="D7" t="n">
-        <v>247</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
@@ -3712,10 +3712,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="D8" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9">
@@ -3728,10 +3728,10 @@
         <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -3744,10 +3744,10 @@
         <v>77</v>
       </c>
       <c r="C10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
@@ -3758,10 +3758,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>650.95</v>
+        <v>651.16</v>
       </c>
       <c r="D12" t="n">
-        <v>773.3099999999999</v>
+        <v>773.28</v>
       </c>
     </row>
     <row r="14">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="18">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>915 – 1087 und</t>
+          <t>912 – 1083 und</t>
         </is>
       </c>
     </row>
@@ -4097,21 +4097,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ajustada: M 25% · S 22% · XS 24.3% (recibe lo restado de M y S).</t>
+          <t xml:space="preserve">   Ajustada: M 25% · S 22% · XS 18.0% (recibe lo restado de M y S).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   XL reforzado +1.5 pp desde L → L 16.2% · XL 11.0%.</t>
+          <t xml:space="preserve">   XL reforzado +1.5 pp desde L → L 16.6% · XL 11.3%.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Núcleo S+M: +0.75 pp a S y a M (igual en chaqueta y pant); resto desde XS/L/XL proporcional.</t>
+          <t xml:space="preserve">   XS objetivo 18%: exceso de XS repartido por igual a S y M (criterio I+D).</t>
         </is>
       </c>
     </row>

--- a/LITE_PANT_RANGO_PRODUCCION.xlsx
+++ b/LITE_PANT_RANGO_PRODUCCION.xlsx
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5485</v>
+        <v>1.5523</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mín · máx 785 und</t>
+          <t>mín · máx 783 und</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mín · máx 298 und</t>
+          <t>mín · máx 297 und</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1288,24 +1288,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L 16.6%</t>
+          <t>L 18.2%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>XS objetivo 18%</t>
+          <t>XS objetivo 15.2%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>XS 18.0%</t>
+          <t>XS 15.2%</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Exceso repartido 50/50 a S y M · L/XL sin cambio</t>
+          <t>+1.6 pp a L · resto 50/50 S y M</t>
         </is>
       </c>
     </row>
@@ -1563,14 +1563,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>164</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>195</v>
       </c>
     </row>
     <row r="6">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7">
@@ -1599,14 +1599,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
@@ -1699,14 +1699,14 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Rango producción: 912 – 1083 und</t>
+          <t>Rango producción: 910 – 1080 und</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>MÍNIMO — 912 und (compromiso)</t>
+          <t>MÍNIMO — 910 und (compromiso)</t>
         </is>
       </c>
     </row>
@@ -1754,22 +1754,22 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>77</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -1779,19 +1779,19 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>229</v>
@@ -1804,28 +1804,28 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>MÁXIMO — 1083 und (techo)</t>
+          <t>MÁXIMO — 1080 und (techo)</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>89</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14">
@@ -1898,22 +1898,22 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="E14" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C14" s="17" t="n">
-        <v>76</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>50</v>
-      </c>
       <c r="F14" s="17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15">
@@ -1923,22 +1923,22 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="17">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>1057.61</v>
+        <v>1057.02</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>1215.64</v>
+        <v>1215.54</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>354.75</v>
+        <v>355.37</v>
       </c>
       <c r="C20" s="23" t="n">
-        <v>461.36</v>
+        <v>461.03</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>1412.36</v>
+        <v>1412.39</v>
       </c>
       <c r="C21" s="23" t="n">
-        <v>1677</v>
+        <v>1676.57</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>651.16</v>
+        <v>651.29</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>773.28</v>
+        <v>773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2141,14 +2141,14 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Rango global: 912 – 1083 und</t>
+          <t>Rango global: 910 – 1080 und</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Negro (785 und máx)</t>
+          <t>Negro (783 und máx)</t>
         </is>
       </c>
     </row>
@@ -2243,28 +2243,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>77</v>
@@ -2280,16 +2280,16 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>Verde Militar (298 und máx)</t>
+          <t>Verde Militar (297 und máx)</t>
         </is>
       </c>
     </row>
@@ -2384,34 +2384,34 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C14" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="I14" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>50</v>
-      </c>
       <c r="J14" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -2424,7 +2424,7 @@
         <v>229</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="19">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C20" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="21">
@@ -2470,7 +2470,7 @@
         <v>229</v>
       </c>
       <c r="C21" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D5" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E5" t="n">
-        <v>1057.61</v>
+        <v>1057.02</v>
       </c>
       <c r="F5" t="n">
-        <v>1215.64</v>
+        <v>1215.54</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1057.61</v>
+        <v>1057.02</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1215.64</v>
+        <v>1215.54</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>121.918</v>
+        <v>121.872</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>140.144</v>
+        <v>140.154</v>
       </c>
     </row>
     <row r="6">
@@ -2630,25 +2630,25 @@
         <v>229</v>
       </c>
       <c r="D6" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E6" t="n">
-        <v>354.75</v>
+        <v>355.37</v>
       </c>
       <c r="F6" t="n">
-        <v>461.36</v>
+        <v>461.03</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>354.75</v>
+        <v>355.37</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>461.36</v>
+        <v>461.03</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>40.914</v>
+        <v>40.958</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>53.175</v>
+        <v>53.165</v>
       </c>
     </row>
     <row r="7">
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D7" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E7" t="n">
-        <v>1412.36</v>
+        <v>1412.39</v>
       </c>
       <c r="F7" t="n">
-        <v>1677</v>
+        <v>1676.57</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1412.36</v>
+        <v>1412.39</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>1677</v>
+        <v>1676.57</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>162.832</v>
+        <v>162.83</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>193.319</v>
@@ -2748,31 +2748,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E11" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
         <v>89</v>
       </c>
       <c r="G11" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="H11" t="n">
-        <v>1215.64</v>
+        <v>1215.54</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1215.64</v>
+        <v>1215.54</v>
       </c>
       <c r="J11" t="n">
-        <v>140.144</v>
+        <v>140.154</v>
       </c>
     </row>
     <row r="12">
@@ -2782,31 +2782,31 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>78</v>
+      </c>
+      <c r="D12" t="n">
+        <v>86</v>
+      </c>
+      <c r="E12" t="n">
         <v>54</v>
       </c>
-      <c r="C12" t="n">
-        <v>76</v>
-      </c>
-      <c r="D12" t="n">
-        <v>85</v>
-      </c>
-      <c r="E12" t="n">
-        <v>50</v>
-      </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>461.36</v>
+        <v>461.03</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>461.36</v>
+        <v>461.03</v>
       </c>
       <c r="J12" t="n">
-        <v>53.175</v>
+        <v>53.165</v>
       </c>
     </row>
     <row r="14">
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>651.16</v>
+        <v>651.29</v>
       </c>
       <c r="C20" t="n">
-        <v>773.28</v>
+        <v>773</v>
       </c>
     </row>
     <row r="21">
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C21" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="23" t="n">
         <v>15</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <v>18</v>
       </c>
       <c r="D5" s="22" t="n">
         <v>22</v>
@@ -3072,22 +3072,22 @@
         <v>26</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>29</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="22" t="n">
         <v>10</v>
       </c>
       <c r="K5" s="23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3097,28 +3097,28 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="C6" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="D6" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>64</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>71</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="I6" s="23" t="n">
         <v>44</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>62</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>59</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>69</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>40</v>
       </c>
       <c r="J6" s="22" t="n">
         <v>23</v>
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="23" t="n">
         <v>22</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <v>26</v>
       </c>
       <c r="D7" s="22" t="n">
         <v>32</v>
@@ -3146,22 +3146,22 @@
         <v>38</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J7" s="22" t="n">
         <v>14</v>
       </c>
       <c r="K7" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="23" t="n">
         <v>18</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <v>22</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>26</v>
@@ -3186,16 +3186,16 @@
         <v>29</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" s="23" t="n">
         <v>14</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="23" t="n">
         <v>19</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <v>22</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>27</v>
@@ -3260,16 +3260,16 @@
         <v>30</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>14</v>
@@ -3282,34 +3282,34 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>22</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="22" t="n">
         <v>25</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J11" s="22" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3319,28 +3319,28 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>13</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>16</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>19</v>
       </c>
       <c r="E12" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="F12" s="22" t="n">
-        <v>21</v>
-      </c>
       <c r="G12" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="22" t="n">
         <v>9</v>
@@ -3356,28 +3356,28 @@
         </is>
       </c>
       <c r="B13" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="C13" s="23" t="n">
-        <v>28</v>
-      </c>
       <c r="D13" s="22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="23" t="n">
         <v>40</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>15</v>
@@ -3393,34 +3393,34 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -3478,7 +3478,7 @@
         <v>206</v>
       </c>
       <c r="C19" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D19" t="n">
         <v>10.7</v>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20" t="n">
         <v>6.4</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
         <v>5.3</v>
@@ -3558,7 +3558,7 @@
         <v>86</v>
       </c>
       <c r="C24" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D24" t="n">
         <v>4.5</v>
@@ -3590,7 +3590,7 @@
         <v>131</v>
       </c>
       <c r="C26" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26" t="n">
         <v>6.8</v>
@@ -3680,10 +3680,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="n">
+        <v>138</v>
+      </c>
+      <c r="D6" t="n">
         <v>164</v>
-      </c>
-      <c r="D6" t="n">
-        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -3696,10 +3696,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D7" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8">
@@ -3712,10 +3712,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D8" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -3728,10 +3728,10 @@
         <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -3758,10 +3758,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>651.16</v>
+        <v>651.29</v>
       </c>
       <c r="D12" t="n">
-        <v>773.28</v>
+        <v>773</v>
       </c>
     </row>
     <row r="14">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="18">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>912 – 1083 und</t>
+          <t>910 – 1080 und</t>
         </is>
       </c>
     </row>
@@ -4097,21 +4097,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ajustada: M 25% · S 22% · XS 18.0% (recibe lo restado de M y S).</t>
+          <t xml:space="preserve">   Ajustada: M 25% · S 22% · XS 15.2% (recibe lo restado de M y S).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   XL reforzado +1.5 pp desde L → L 16.6% · XL 11.3%.</t>
+          <t xml:space="preserve">   XL reforzado +1.5 pp desde L → L 18.2% · XL 11.3%.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   XS objetivo 18%: exceso de XS repartido por igual a S y M (criterio I+D).</t>
+          <t xml:space="preserve">   XS objetivo 15.2%: +1.6 pp a L; excedente repartido entre S y M.</t>
         </is>
       </c>
     </row>
